--- a/tracking_forms/029_fitness_logger_form--tracking_forms.xlsx
+++ b/tracking_forms/029_fitness_logger_form--tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -799,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'strength'}</t>
+          <t>strength</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'Strength'}</t>
+          <t>Strength</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'cardio'}</t>
+          <t>cardio</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'Cardio'}</t>
+          <t>Cardio</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'flexibility'}</t>
+          <t>flexibility</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'Flexibility'}</t>
+          <t>Flexibility</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'endurance'}</t>
+          <t>endurance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'Endurance'}</t>
+          <t>Endurance</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'core'}</t>
+          <t>core</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'Core'}</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'power'}</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'Power'}</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'balance'}</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'Balance'}</t>
+          <t>Balance</t>
         </is>
       </c>
     </row>
@@ -951,131 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'flexibility'}</t>
+          <t>stretching</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'Flexibility'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'name':_'stretching'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'name': 'Stretching'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>{'name':_'balance'}</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{'name': 'Balance'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'name':_'core'}</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{'name': 'Core'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'name':_'endurance'}</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{'name': 'Endurance'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'name':_'strength'}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{'name': 'Strength'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'name':_'power'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'name': 'Power'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'name':_'cardio'}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'name': 'Cardio'}</t>
+          <t>Stretching</t>
         </is>
       </c>
     </row>
